--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N90_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N90_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54.09130661596618</v>
+        <v>8.789837325094505</v>
       </c>
       <c r="D2" t="n">
-        <v>17.85411841775514</v>
+        <v>2.90129424288521</v>
       </c>
       <c r="E2" t="n">
-        <v>10.42402504749112</v>
+        <v>1.693904070217307</v>
       </c>
       <c r="F2" t="n">
-        <v>10.61865357383645</v>
+        <v>1.725531205748424</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.50049730509527</v>
+        <v>5.28133081207798</v>
       </c>
       <c r="D3" t="n">
-        <v>32.78077386291297</v>
+        <v>5.326875752723357</v>
       </c>
       <c r="E3" t="n">
-        <v>10.42402504749112</v>
+        <v>1.693904070217307</v>
       </c>
       <c r="F3" t="n">
-        <v>10.61865357383645</v>
+        <v>1.725531205748424</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.34020807784654</v>
+        <v>3.955283812650063</v>
       </c>
       <c r="D4" t="n">
-        <v>24.88730752321033</v>
+        <v>4.044187472521679</v>
       </c>
       <c r="E4" t="n">
-        <v>10.42402504749112</v>
+        <v>1.693904070217307</v>
       </c>
       <c r="F4" t="n">
-        <v>10.61865357383645</v>
+        <v>1.725531205748424</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.65237392711744</v>
+        <v>5.956010763156585</v>
       </c>
       <c r="D5" t="n">
-        <v>36.922402498653</v>
+        <v>5.999890406031112</v>
       </c>
       <c r="E5" t="n">
-        <v>10.42402504749112</v>
+        <v>1.693904070217307</v>
       </c>
       <c r="F5" t="n">
-        <v>10.61865357383645</v>
+        <v>1.725531205748424</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.74809620102031</v>
+        <v>4.8340656326658</v>
       </c>
       <c r="D6" t="n">
-        <v>29.28392931970263</v>
+        <v>4.758638514451678</v>
       </c>
       <c r="E6" t="n">
-        <v>10.42402504749112</v>
+        <v>1.693904070217307</v>
       </c>
       <c r="F6" t="n">
-        <v>10.61865357383645</v>
+        <v>1.725531205748424</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.74299378889545</v>
+        <v>7.75823649069551</v>
       </c>
       <c r="D7" t="n">
-        <v>46.38551904743161</v>
+        <v>7.537646845207638</v>
       </c>
       <c r="E7" t="n">
-        <v>10.42402504749112</v>
+        <v>1.693904070217307</v>
       </c>
       <c r="F7" t="n">
-        <v>10.61865357383645</v>
+        <v>1.725531205748424</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.26028809038891</v>
+        <v>6.054796814688198</v>
       </c>
       <c r="D8" t="n">
-        <v>36.64383305248902</v>
+        <v>5.954622871029466</v>
       </c>
       <c r="E8" t="n">
-        <v>10.42402504749112</v>
+        <v>1.693904070217307</v>
       </c>
       <c r="F8" t="n">
-        <v>10.61865357383645</v>
+        <v>1.725531205748424</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.32695607241987</v>
+        <v>7.365630361768229</v>
       </c>
       <c r="D9" t="n">
-        <v>43.55306680412951</v>
+        <v>7.077373355671046</v>
       </c>
       <c r="E9" t="n">
-        <v>10.42402504749112</v>
+        <v>1.693904070217307</v>
       </c>
       <c r="F9" t="n">
-        <v>10.61865357383645</v>
+        <v>1.725531205748424</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>56.35717195669391</v>
+        <v>9.158040442962761</v>
       </c>
       <c r="D10" t="n">
-        <v>54.45438873689599</v>
+        <v>8.848838169745598</v>
       </c>
       <c r="E10" t="n">
-        <v>10.42402504749112</v>
+        <v>1.693904070217307</v>
       </c>
       <c r="F10" t="n">
-        <v>10.61865357383645</v>
+        <v>1.725531205748424</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
